--- a/output/pdf_financials_xlsx/NCX.xlsx
+++ b/output/pdf_financials_xlsx/NCX.xlsx
@@ -1177,49 +1177,49 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>0.789303</v>
+        <v>-0.789303</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>8.196759999999999</v>
+        <v>-8.196759999999999</v>
       </c>
       <c r="D16" s="3" t="n">
-        <v>0.735403</v>
+        <v>-0.735403</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>0.675419</v>
+        <v>-0.675419</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>0.42869</v>
+        <v>-0.42869</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>0.565244</v>
+        <v>-0.565244</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>1.508709</v>
+        <v>-1.508709</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>0.429761</v>
+        <v>-0.429761</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>0.302413</v>
+        <v>-0.302413</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>1.192791</v>
+        <v>-1.192791</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>5.22591</v>
+        <v>-5.22591</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>6.663366</v>
+        <v>-6.663366</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>5.348612</v>
+        <v>-5.348612</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>9.506174</v>
+        <v>-9.506174</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>13.483659</v>
+        <v>-13.483659</v>
       </c>
     </row>
     <row r="17">
@@ -1445,49 +1445,49 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>0.789303</v>
+        <v>-0.789303</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>8.196759999999999</v>
+        <v>-8.196759999999999</v>
       </c>
       <c r="D20" s="3" t="n">
-        <v>0.735403</v>
+        <v>-0.735403</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>0.675419</v>
+        <v>-0.675419</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>0.42869</v>
+        <v>-0.42869</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>0.565244</v>
+        <v>-0.565244</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>1.508709</v>
+        <v>-1.508709</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>0.429761</v>
+        <v>-0.429761</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>0.302413</v>
+        <v>-0.302413</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>1.192791</v>
+        <v>-1.192791</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>5.22591</v>
+        <v>-5.22591</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>6.663366</v>
+        <v>-6.663366</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>5.348612</v>
+        <v>-5.348612</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>9.506174</v>
+        <v>-9.506174</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>13.483659</v>
+        <v>-13.483659</v>
       </c>
     </row>
     <row r="21">
@@ -1601,49 +1601,49 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>0.789303</v>
+        <v>-0.789303</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>8.196759999999999</v>
+        <v>-8.196759999999999</v>
       </c>
       <c r="D23" s="3" t="n">
-        <v>0.735403</v>
+        <v>-0.735403</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>0.675419</v>
+        <v>-0.675419</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>0.42869</v>
+        <v>-0.42869</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>0.565244</v>
+        <v>-0.565244</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>1.508709</v>
+        <v>-1.508709</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>0.429761</v>
+        <v>-0.429761</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>0.302413</v>
+        <v>-0.302413</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>1.192791</v>
+        <v>-1.192791</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>5.22591</v>
+        <v>-5.22591</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>6.663366</v>
+        <v>-6.663366</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>5.348612</v>
+        <v>-5.348612</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>9.506174</v>
+        <v>-9.506174</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>13.483659</v>
+        <v>-13.483659</v>
       </c>
     </row>
     <row r="24">
@@ -1757,10 +1757,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>23.214794</v>
+        <v>-23.214794</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>54.645067</v>
+        <v>-54.645067</v>
       </c>
       <c r="D26" s="1" t="inlineStr">
         <is>
@@ -1783,7 +1783,7 @@
         </is>
       </c>
       <c r="H26" s="3" t="n">
-        <v>107.764929</v>
+        <v>-107.764929</v>
       </c>
       <c r="I26" s="1" t="inlineStr">
         <is>
@@ -1801,19 +1801,19 @@
         </is>
       </c>
       <c r="L26" s="3" t="n">
-        <v>174.197</v>
+        <v>-174.197</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>222.1122</v>
+        <v>-222.1122</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>178.287067</v>
+        <v>-178.287067</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>237.65435</v>
+        <v>-237.65435</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>269.67318</v>
+        <v>-269.67318</v>
       </c>
     </row>
     <row r="27">
@@ -1823,49 +1823,49 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>0.789303</v>
+        <v>-0.789303</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>8.196759999999999</v>
+        <v>-8.196759999999999</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>0.735403</v>
+        <v>-0.735403</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>0.675419</v>
+        <v>-0.675419</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>0.42869</v>
+        <v>-0.42869</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>0.565244</v>
+        <v>-0.565244</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>1.508709</v>
+        <v>-1.508709</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>0.429761</v>
+        <v>-0.429761</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>0.302413</v>
+        <v>-0.302413</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>1.192791</v>
+        <v>-1.192791</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>5.22591</v>
+        <v>-5.22591</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>6.663366</v>
+        <v>-6.663366</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>5.348612</v>
+        <v>-5.348612</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>9.506174</v>
+        <v>-9.506174</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>13.483659</v>
+        <v>-13.483659</v>
       </c>
     </row>
     <row r="28">
@@ -1927,49 +1927,49 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>0.789303</v>
+        <v>-0.789303</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>8.196759999999999</v>
+        <v>-8.196759999999999</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>0.735403</v>
+        <v>-0.735403</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>0.675419</v>
+        <v>-0.675419</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>0.42869</v>
+        <v>-0.42869</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>0.565244</v>
+        <v>-0.565244</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>1.508709</v>
+        <v>-1.508709</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>0.429761</v>
+        <v>-0.429761</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>0.302413</v>
+        <v>-0.302413</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>1.192791</v>
+        <v>-1.192791</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>5.22591</v>
+        <v>-5.22591</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>6.663366</v>
+        <v>-6.663366</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>5.348612</v>
+        <v>-5.348612</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>9.506174</v>
+        <v>-9.506174</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>13.483659</v>
+        <v>-13.483659</v>
       </c>
     </row>
     <row r="30">
@@ -2061,49 +2061,49 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -5402,31 +5402,31 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.42433</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.8356749999999999</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.880412</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.04276</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.07394</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>1.034582</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>1.430663</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>1.610949</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>0.410876</v>
       </c>
       <c r="K92" s="3" t="n">
         <v>2.328358</v>
@@ -12652,7 +12652,11 @@
           <t>Warrant reserves</t>
         </is>
       </c>
-      <c r="D57" t="inlineStr"/>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E57" t="inlineStr">
         <is>
           <t>-</t>
@@ -12990,7 +12994,11 @@
           <t>Reserves (Note 8)</t>
         </is>
       </c>
-      <c r="D61" t="inlineStr"/>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E61" t="inlineStr">
         <is>
           <t>-</t>
@@ -13164,7 +13172,11 @@
           <t>Reserves (Note 9)</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr"/>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E63" t="inlineStr">
         <is>
           <t>-</t>
@@ -13789,7 +13801,11 @@
           <t>Reserves (Note 10)</t>
         </is>
       </c>
-      <c r="D70" t="inlineStr"/>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
         <v>0.42433</v>
       </c>
@@ -14246,7 +14262,11 @@
           <t>Reserves (Note 11)</t>
         </is>
       </c>
-      <c r="D75" t="inlineStr"/>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E75" s="5" t="n">
         <v>0.42433</v>
       </c>
@@ -31104,22 +31124,22 @@
         </is>
       </c>
       <c r="N264" s="5" t="n">
-        <v>1.192791</v>
+        <v>-1.192791</v>
       </c>
       <c r="O264" s="5" t="n">
-        <v>5.22591</v>
+        <v>-5.22591</v>
       </c>
       <c r="P264" s="5" t="n">
-        <v>6.663366</v>
+        <v>-6.663366</v>
       </c>
       <c r="Q264" s="5" t="n">
-        <v>5.348612</v>
+        <v>-5.348612</v>
       </c>
       <c r="R264" s="5" t="n">
-        <v>9.506174</v>
+        <v>-9.506174</v>
       </c>
       <c r="S264" s="5" t="n">
-        <v>13.483659</v>
+        <v>-13.483659</v>
       </c>
     </row>
     <row r="265">
@@ -33983,34 +34003,34 @@
         </is>
       </c>
       <c r="E298" s="5" t="n">
-        <v>0.789303</v>
+        <v>-0.789303</v>
       </c>
       <c r="F298" s="5" t="n">
-        <v>8.196759999999999</v>
+        <v>-8.196759999999999</v>
       </c>
       <c r="G298" s="5" t="n">
-        <v>0.735403</v>
+        <v>-0.735403</v>
       </c>
       <c r="H298" s="5" t="n">
-        <v>0.675419</v>
+        <v>-0.675419</v>
       </c>
       <c r="I298" s="5" t="n">
-        <v>0.42869</v>
+        <v>-0.42869</v>
       </c>
       <c r="J298" s="5" t="n">
-        <v>0.565244</v>
+        <v>-0.565244</v>
       </c>
       <c r="K298" s="5" t="n">
-        <v>1.508709</v>
+        <v>-1.508709</v>
       </c>
       <c r="L298" s="5" t="n">
-        <v>0.429761</v>
+        <v>-0.429761</v>
       </c>
       <c r="M298" s="5" t="n">
-        <v>0.302413</v>
+        <v>-0.302413</v>
       </c>
       <c r="N298" s="5" t="n">
-        <v>1.192791</v>
+        <v>-1.192791</v>
       </c>
       <c r="O298" t="inlineStr">
         <is>
@@ -35649,22 +35669,22 @@
         </is>
       </c>
       <c r="H317" s="5" t="n">
-        <v>0.675419</v>
+        <v>-0.675419</v>
       </c>
       <c r="I317" s="5" t="n">
-        <v>0.42869</v>
+        <v>-0.42869</v>
       </c>
       <c r="J317" s="5" t="n">
-        <v>0.565244</v>
+        <v>-0.565244</v>
       </c>
       <c r="K317" s="5" t="n">
-        <v>1.508709</v>
+        <v>-1.508709</v>
       </c>
       <c r="L317" s="5" t="n">
-        <v>0.429761</v>
+        <v>-0.429761</v>
       </c>
       <c r="M317" s="5" t="n">
-        <v>0.302413</v>
+        <v>-0.302413</v>
       </c>
       <c r="N317" t="inlineStr">
         <is>
@@ -39012,13 +39032,13 @@
         </is>
       </c>
       <c r="F356" s="5" t="n">
-        <v>8.196759999999999</v>
+        <v>-8.196759999999999</v>
       </c>
       <c r="G356" s="5" t="n">
-        <v>0.735403</v>
+        <v>-0.735403</v>
       </c>
       <c r="H356" s="5" t="n">
-        <v>0.675419</v>
+        <v>-0.675419</v>
       </c>
       <c r="I356" t="inlineStr">
         <is>
@@ -40708,10 +40728,10 @@
         </is>
       </c>
       <c r="E375" s="5" t="n">
-        <v>0.789303</v>
+        <v>-0.789303</v>
       </c>
       <c r="F375" s="5" t="n">
-        <v>8.196759999999999</v>
+        <v>-8.196759999999999</v>
       </c>
       <c r="G375" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/NCX.xlsx
+++ b/output/pdf_financials_xlsx/NCX.xlsx
@@ -969,49 +969,49 @@
         </is>
       </c>
       <c r="B12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003196</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>-0.004656</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00062</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00305</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>0</v>
+        <v>-0.000615</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001462</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00249</v>
       </c>
       <c r="I12" s="3" t="n">
-        <v>0</v>
+        <v>-0.002522</v>
       </c>
       <c r="J12" s="3" t="n">
-        <v>0</v>
+        <v>-0.003473</v>
       </c>
       <c r="K12" s="3" t="n">
-        <v>0</v>
+        <v>-0.001713</v>
       </c>
       <c r="L12" s="3" t="n">
-        <v>0</v>
+        <v>-0.00809</v>
       </c>
       <c r="M12" s="3" t="n">
-        <v>0</v>
+        <v>-0.050473</v>
       </c>
       <c r="N12" s="3" t="n">
-        <v>0</v>
+        <v>-0.180626</v>
       </c>
       <c r="O12" s="3" t="n">
-        <v>0</v>
+        <v>-0.230832</v>
       </c>
       <c r="P12" s="3" t="n">
-        <v>0</v>
+        <v>-0.477702</v>
       </c>
     </row>
     <row r="13">
@@ -1823,49 +1823,49 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>-0.789303</v>
+        <v>-0.786107</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-8.196759999999999</v>
+        <v>-8.192104</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.735403</v>
+        <v>-0.734783</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.675419</v>
+        <v>-0.672369</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>-0.42869</v>
+        <v>-0.428075</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-0.565244</v>
+        <v>-0.563782</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.508709</v>
+        <v>-1.506219</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>-0.429761</v>
+        <v>-0.427239</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>-0.302413</v>
+        <v>-0.29894</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>-1.192791</v>
+        <v>-1.191078</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>-5.22591</v>
+        <v>-5.21782</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>-6.663366</v>
+        <v>-6.612893</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>-5.348612</v>
+        <v>-5.167986</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>-9.506174</v>
+        <v>-9.275342</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>-13.483659</v>
+        <v>-13.005957</v>
       </c>
     </row>
     <row r="28">
@@ -1927,49 +1927,49 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>-0.789303</v>
+        <v>-0.786107</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-8.196759999999999</v>
+        <v>-8.192104</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.735403</v>
+        <v>-0.734783</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.675419</v>
+        <v>-0.672369</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>-0.42869</v>
+        <v>-0.428075</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-0.565244</v>
+        <v>-0.563782</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.508709</v>
+        <v>-1.506219</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-0.429761</v>
+        <v>-0.427239</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-0.302413</v>
+        <v>-0.29894</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-1.192791</v>
+        <v>-1.191078</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-5.22591</v>
+        <v>-5.21782</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-6.663366</v>
+        <v>-6.612893</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>-5.348612</v>
+        <v>-5.167986</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>-9.506174</v>
+        <v>-9.275342</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>-13.483659</v>
+        <v>-13.005957</v>
       </c>
     </row>
     <row r="30">
@@ -2202,34 +2202,34 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>1.908108</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.588152</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.028693</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.142972</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.207055</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.571582</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.527532</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.806724</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.37888</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>2.942711</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>5.794741</v>
@@ -2306,34 +2306,34 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>1.908108</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.588152</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.028693</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.142972</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.207055</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.571582</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.527532</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.806724</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.37888</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>2.942711</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>5.902911</v>
@@ -2930,34 +2930,34 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>2.032755</v>
+        <v>0.124647</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.647481</v>
+        <v>0.059329</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.069643</v>
+        <v>0.04095</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.195422</v>
+        <v>0.05245</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.246517</v>
+        <v>0.039462</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.609903</v>
+        <v>0.038321</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.549053</v>
+        <v>0.021521</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.905531</v>
+        <v>0.09880700000000001</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.769893</v>
+        <v>0.391013</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>2.968703</v>
+        <v>0.025992</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>0.471192</v>
@@ -7104,10 +7104,10 @@
         <v>0</v>
       </c>
       <c r="O124" s="3" t="n">
-        <v>0</v>
+        <v>-0.036306</v>
       </c>
       <c r="P124" s="3" t="n">
-        <v>0</v>
+        <v>-0.107423</v>
       </c>
     </row>
     <row r="125">
@@ -7156,10 +7156,10 @@
         <v>0</v>
       </c>
       <c r="O125" s="3" t="n">
-        <v>0</v>
+        <v>-0.036306</v>
       </c>
       <c r="P125" s="3" t="n">
-        <v>0</v>
+        <v>-0.107423</v>
       </c>
     </row>
     <row r="126">
@@ -8332,7 +8332,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -11458,7 +11462,7 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -11646,7 +11650,7 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E45" s="5" t="n">
@@ -12043,7 +12047,11 @@
           <t>Reclamation deposits</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>RestrictedCash</t>
+        </is>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
           <t>-</t>
@@ -16099,7 +16107,11 @@
           <t>Lease payments 10</t>
         </is>
       </c>
-      <c r="D96" t="inlineStr"/>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E96" t="inlineStr">
         <is>
           <t>-</t>
@@ -18886,7 +18898,11 @@
           <t>Lease payments 8</t>
         </is>
       </c>
-      <c r="D127" t="inlineStr"/>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
           <t>-</t>
@@ -30901,7 +30917,7 @@
       </c>
       <c r="D262" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E262" t="inlineStr">
@@ -33742,7 +33758,7 @@
       </c>
       <c r="D295" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E295" s="5" t="n">
@@ -37342,7 +37358,7 @@
       </c>
       <c r="D337" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E337" t="inlineStr">
@@ -38928,7 +38944,7 @@
       </c>
       <c r="D355" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E355" t="inlineStr">

--- a/output/pdf_financials_xlsx/NCX.xlsx
+++ b/output/pdf_financials_xlsx/NCX.xlsx
@@ -6375,10 +6375,10 @@
         </is>
       </c>
       <c r="B111" s="3" t="n">
-        <v>0</v>
+        <v>-0.022765</v>
       </c>
       <c r="C111" s="3" t="n">
-        <v>0</v>
+        <v>-0.012995</v>
       </c>
       <c r="D111" s="3" t="n">
         <v>0</v>
@@ -6405,7 +6405,7 @@
         <v>0</v>
       </c>
       <c r="L111" s="3" t="n">
-        <v>0</v>
+        <v>-0.146396</v>
       </c>
       <c r="M111" s="3" t="n">
         <v>0</v>
@@ -6417,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="P111" s="3" t="n">
-        <v>0</v>
+        <v>-0.307655</v>
       </c>
     </row>
     <row r="112">
@@ -7649,10 +7649,10 @@
         </is>
       </c>
       <c r="B134" s="3" t="n">
-        <v>0</v>
+        <v>-0.022765</v>
       </c>
       <c r="C134" s="3" t="n">
-        <v>0</v>
+        <v>-0.012995</v>
       </c>
       <c r="D134" s="3" t="n">
         <v>0</v>
@@ -7679,7 +7679,7 @@
         <v>0</v>
       </c>
       <c r="L134" s="3" t="n">
-        <v>0</v>
+        <v>-0.146396</v>
       </c>
       <c r="M134" s="3" t="n">
         <v>0</v>
@@ -7691,7 +7691,7 @@
         <v>0</v>
       </c>
       <c r="P134" s="3" t="n">
-        <v>0</v>
+        <v>-0.307655</v>
       </c>
     </row>
     <row r="135">
@@ -7701,10 +7701,10 @@
         </is>
       </c>
       <c r="B135" s="3" t="n">
-        <v>-0.569127</v>
+        <v>-0.591892</v>
       </c>
       <c r="C135" s="3" t="n">
-        <v>-3.701751</v>
+        <v>-3.714746</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -7771,7 +7771,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S389"/>
+  <dimension ref="A1:S397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15395,7 +15395,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -15840,7 +15844,11 @@
           <t>Private placement 11</t>
         </is>
       </c>
-      <c r="D93" t="inlineStr"/>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E93" t="inlineStr">
         <is>
           <t>-</t>
@@ -18631,7 +18639,11 @@
           <t>Private placement 9</t>
         </is>
       </c>
-      <c r="D124" t="inlineStr"/>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
           <t>-</t>
@@ -20443,7 +20455,11 @@
           <t>Private placement 7</t>
         </is>
       </c>
-      <c r="D144" t="inlineStr"/>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E144" t="inlineStr">
         <is>
           <t>-</t>
@@ -22332,7 +22348,11 @@
           <t>Private placement 6</t>
         </is>
       </c>
-      <c r="D165" t="inlineStr"/>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>CommonStockIssuance</t>
+        </is>
+      </c>
       <c r="E165" t="inlineStr">
         <is>
           <t>-</t>
@@ -24700,7 +24720,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D191" t="inlineStr"/>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E191" t="inlineStr">
         <is>
           <t>-</t>
@@ -29230,7 +29254,11 @@
           <t>Purchase of equipment</t>
         </is>
       </c>
-      <c r="D243" t="inlineStr"/>
+      <c r="D243" t="inlineStr">
+        <is>
+          <t>PurchaseOfPPE</t>
+        </is>
+      </c>
       <c r="E243" s="5" t="n">
         <v>-0.022765</v>
       </c>
@@ -32765,10 +32793,8 @@
           <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
-      <c r="E283" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E283" s="5" t="n">
+        <v>0.005921</v>
       </c>
       <c r="F283" t="inlineStr">
         <is>
@@ -35669,10 +35695,8 @@
           <t>NetIncome</t>
         </is>
       </c>
-      <c r="E317" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E317" s="5" t="n">
+        <v>-0.400153</v>
       </c>
       <c r="F317" t="inlineStr">
         <is>
@@ -38591,10 +38615,8 @@
         </is>
       </c>
       <c r="D351" t="inlineStr"/>
-      <c r="E351" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E351" s="5" t="n">
+        <v>0.42433</v>
       </c>
       <c r="F351" s="5" t="n">
         <v>0.174177</v>
@@ -39218,10 +39240,8 @@
         </is>
       </c>
       <c r="D358" t="inlineStr"/>
-      <c r="E358" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E358" s="5" t="n">
+        <v>0.150105</v>
       </c>
       <c r="F358" s="5" t="n">
         <v>0.210117</v>
@@ -42020,6 +42040,744 @@
         </is>
       </c>
       <c r="S389" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Expenses</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>Amortization $</t>
+        </is>
+      </c>
+      <c r="D390" t="inlineStr">
+        <is>
+          <t>Amortization</t>
+        </is>
+      </c>
+      <c r="E390" s="5" t="n">
+        <v>0.001495</v>
+      </c>
+      <c r="F390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S390" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>DEFICIT, BEGINNING OF PERIOD $</t>
+        </is>
+      </c>
+      <c r="D391" t="inlineStr"/>
+      <c r="E391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S391" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>DEFICIT, END OF PERIOD $</t>
+        </is>
+      </c>
+      <c r="D392" t="inlineStr"/>
+      <c r="E392" s="5" t="n">
+        <v>0.400153</v>
+      </c>
+      <c r="F392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S392" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>RESERVES, BEGINNING OF PERIOD (Note 10) $</t>
+        </is>
+      </c>
+      <c r="D393" t="inlineStr"/>
+      <c r="E393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S393" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>RESERVES, END OF PERIOD $</t>
+        </is>
+      </c>
+      <c r="D394" t="inlineStr"/>
+      <c r="E394" s="5" t="n">
+        <v>0.42433</v>
+      </c>
+      <c r="F394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S394" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>SHARE CAPITAL, BEGINNING OF PERIOD (Note 9) $</t>
+        </is>
+      </c>
+      <c r="D395" t="inlineStr"/>
+      <c r="E395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S395" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>Issued pursuant to plan of arrangement (Note 5)</t>
+        </is>
+      </c>
+      <c r="D396" t="inlineStr"/>
+      <c r="E396" s="5" t="n">
+        <v>16.778892</v>
+      </c>
+      <c r="F396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S396" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>WEIGHTED AVERAGE NUMBER</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>SHARE CAPITAL, END OF PERIOD $</t>
+        </is>
+      </c>
+      <c r="D397" t="inlineStr"/>
+      <c r="E397" s="5" t="n">
+        <v>16.778892</v>
+      </c>
+      <c r="F397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="I397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="J397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="L397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="M397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="O397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="P397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="Q397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="R397" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="S397" t="inlineStr">
         <is>
           <t>-</t>
         </is>
